--- a/ig/StructureDefinition-as-dr-healthcareservice-social-equipment.xlsx
+++ b/ig/StructureDefinition-as-dr-healthcareservice-social-equipment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T13:25:16+00:00</t>
+    <t>2024-04-25T11:50:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/StructureDefinition-as-dr-healthcareservice-social-equipment.xlsx
+++ b/ig/StructureDefinition-as-dr-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T11:50:43+00:00</t>
+    <t>2024-04-26T07:42:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
